--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2016/NEW_HAMPSHIRE_2016.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2016/NEW_HAMPSHIRE_2016.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Tenejapa</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -470,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -501,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Comala</t>
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -527,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Villa de Álvarez</t>
+          <t>Villa De Álvarez</t>
         </is>
       </c>
       <c r="C12">
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Total</t>
@@ -555,7 +595,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -571,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Total</t>
@@ -654,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -667,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Total</t>
@@ -682,12 +757,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C23">
@@ -698,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Total</t>
@@ -729,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -742,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Cortazar</t>
@@ -755,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>León</t>
@@ -768,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -781,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -794,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Villagrán</t>
@@ -807,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Total</t>
@@ -827,7 +942,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C33">
@@ -838,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Acatepec</t>
@@ -851,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Atlamajalcingo del Monte</t>
+          <t>Atlamajalcingo Del Monte</t>
         </is>
       </c>
       <c r="C35">
@@ -864,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Atlixtac</t>
@@ -877,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -890,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C38">
@@ -903,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -916,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C40">
@@ -929,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C41">
@@ -942,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -955,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -968,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -981,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C45">
@@ -994,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1025,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -1038,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Progreso de Obregón</t>
+          <t>Progreso De Obregón</t>
         </is>
       </c>
       <c r="C49">
@@ -1051,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1082,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C52">
@@ -1095,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C53">
@@ -1108,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Tecalitlán</t>
@@ -1121,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Tomatlán</t>
@@ -1134,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Tuxcacuesco</t>
@@ -1147,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C57">
@@ -1160,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -1173,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1204,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Jungapeo</t>
@@ -1217,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -1230,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Taretan</t>
@@ -1243,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -1256,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -1269,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1300,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -1313,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Mazatepec</t>
@@ -1326,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Tepalcingo</t>
@@ -1339,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1370,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1401,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1432,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Santa Lucía Monteverde</t>
@@ -1445,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Santo Domingo de Morelos</t>
+          <t>Santo Domingo De Morelos</t>
         </is>
       </c>
       <c r="C78">
@@ -1458,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1489,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1502,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Teopantlán</t>
@@ -1515,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -1528,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Xiutetelco</t>
@@ -1541,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1561,7 +1896,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Amealco de Bonfil</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C86">
@@ -1572,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C87">
@@ -1585,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>El Marqués</t>
@@ -1598,9 +1943,14 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C89">
@@ -1611,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -1624,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Tequisquiapan</t>
@@ -1637,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1657,7 +2022,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Axtla de Terrazas</t>
+          <t>Axtla De Terrazas</t>
         </is>
       </c>
       <c r="C93">
@@ -1668,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Charcas</t>
@@ -1681,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -1694,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -1707,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Xilitla</t>
@@ -1720,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1751,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1782,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1813,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -1826,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -1839,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1870,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1901,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C110">
@@ -1914,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -1927,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Soteapan</t>
@@ -1940,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -1953,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Zongolica</t>
@@ -1966,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1997,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -2010,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Miguel Auza</t>
@@ -2023,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Sain Alto</t>
@@ -2036,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -2049,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2072,76 +2547,6 @@
       </c>
       <c r="D122">
         <v>1</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 814,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Marzo de 2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
